--- a/turni.xlsx
+++ b/turni.xlsx
@@ -11,13 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
-  <si>
-    <t>Nome</t>
-  </si>
-  <si>
-    <t>Username Telegram</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
   <si>
     <t>Data</t>
   </si>
@@ -64,21 +58,18 @@
     <t>Ronda</t>
   </si>
   <si>
+    <t>Angelo</t>
+  </si>
+  <si>
+    <t>Alessia</t>
+  </si>
+  <si>
+    <t>Rav; Giacomo</t>
+  </si>
+  <si>
     <t>Luigi</t>
   </si>
   <si>
-    <t>@Luigiwang</t>
-  </si>
-  <si>
-    <t>Angelo</t>
-  </si>
-  <si>
-    <t>Alessia</t>
-  </si>
-  <si>
-    <t>Rav; Giacomo</t>
-  </si>
-  <si>
     <t>Rav</t>
   </si>
   <si>
@@ -88,28 +79,16 @@
     <t>Alessia; Luigi</t>
   </si>
   <si>
-    <t>@RavCheng</t>
-  </si>
-  <si>
     <t>Luigi; Rav</t>
   </si>
   <si>
     <t>Angelo; Rav</t>
   </si>
   <si>
-    <t>@angelopan</t>
-  </si>
-  <si>
     <t>Giacomo; Angelo; Alessia</t>
   </si>
   <si>
     <t>Giacomo; Luigi</t>
-  </si>
-  <si>
-    <t>@GiacJ</t>
-  </si>
-  <si>
-    <t>@Alessia_wang</t>
   </si>
 </sst>
 </file>
@@ -188,10 +167,10 @@
     <xf numFmtId="49" fontId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="59" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="59" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1249,31 +1228,31 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="3" width="17.6719" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.8516" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1719" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.35156" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.85156" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5" style="1" customWidth="1"/>
-    <col min="10" max="13" width="7.67188" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.8516" style="1" customWidth="1"/>
-    <col min="15" max="16" width="9.85156" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.3516" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="12.6719" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6719" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.8516" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1719" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.35156" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85156" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="1" customWidth="1"/>
+    <col min="8" max="11" width="7.67188" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.8516" style="1" customWidth="1"/>
+    <col min="13" max="14" width="9.85156" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.3516" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="12.6719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="B1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="2">
+      <c r="C1" t="s" s="3">
         <v>2</v>
       </c>
       <c r="D1" t="s" s="3">
@@ -1312,213 +1291,177 @@
       <c r="O1" t="s" s="3">
         <v>14</v>
       </c>
-      <c r="P1" t="s" s="3">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s" s="3">
-        <v>16</v>
-      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" t="s" s="4">
+      <c r="A2" s="4">
+        <v>46187</v>
+      </c>
+      <c r="B2" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s" s="5">
         <v>17</v>
       </c>
-      <c r="B2" t="s" s="4">
+      <c r="E2" t="s" s="5">
         <v>18</v>
       </c>
-      <c r="C2" s="5">
-        <v>46187</v>
-      </c>
-      <c r="D2" t="s" s="4">
+      <c r="F2" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="5">
         <v>19</v>
       </c>
-      <c r="E2" t="s" s="4">
+      <c r="H2" t="s" s="5">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s" s="5">
         <v>20</v>
       </c>
-      <c r="F2" t="s" s="4">
+      <c r="J2" t="s" s="5">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s" s="5">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s" s="5">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" t="s" s="5">
         <v>21</v>
-      </c>
-      <c r="G2" t="s" s="4">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s" s="4">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s" s="4">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s" s="4">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s" s="4">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s" s="4">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s" s="4">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s" s="4">
-        <v>17</v>
-      </c>
-      <c r="O2" t="s" s="4">
-        <v>19</v>
-      </c>
-      <c r="P2" s="6"/>
-      <c r="Q2" t="s" s="4">
-        <v>24</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" t="s" s="4">
+      <c r="A3" s="4">
+        <v>46194</v>
+      </c>
+      <c r="B3" t="s" s="5">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s" s="5">
         <v>22</v>
       </c>
-      <c r="B3" t="s" s="4">
-        <v>25</v>
-      </c>
-      <c r="C3" s="5">
-        <v>46194</v>
-      </c>
-      <c r="D3" t="s" s="4">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s" s="4">
+      <c r="E3" t="s" s="5">
         <v>20</v>
       </c>
-      <c r="F3" t="s" s="4">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s" s="4">
+      <c r="F3" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="5">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="5">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s" s="5">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s" s="5">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s" s="5">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="N3" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="O3" t="s" s="5">
         <v>23</v>
-      </c>
-      <c r="H3" t="s" s="4">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s" s="4">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s" s="4">
-        <v>17</v>
-      </c>
-      <c r="K3" t="s" s="4">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s" s="4">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s" s="4">
-        <v>22</v>
-      </c>
-      <c r="O3" t="s" s="4">
-        <v>19</v>
-      </c>
-      <c r="P3" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="s" s="4">
-        <v>27</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" t="s" s="4">
+      <c r="A4" s="4">
+        <v>46201</v>
+      </c>
+      <c r="B4" t="s" s="5">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s" s="5">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s" s="5">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="5">
         <v>19</v>
       </c>
-      <c r="B4" t="s" s="4">
-        <v>28</v>
-      </c>
-      <c r="C4" s="5">
-        <v>46201</v>
-      </c>
-      <c r="D4" t="s" s="4">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s" s="4">
+      <c r="H4" t="s" s="5">
+        <v>18</v>
+      </c>
+      <c r="I4" t="s" s="5">
         <v>20</v>
       </c>
-      <c r="F4" t="s" s="4">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s" s="4">
+      <c r="J4" t="s" s="5">
         <v>19</v>
       </c>
-      <c r="H4" t="s" s="4">
+      <c r="K4" t="s" s="5">
         <v>19</v>
       </c>
-      <c r="I4" t="s" s="4">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s" s="4">
-        <v>17</v>
-      </c>
-      <c r="K4" t="s" s="4">
-        <v>23</v>
-      </c>
-      <c r="L4" t="s" s="4">
-        <v>22</v>
-      </c>
-      <c r="M4" t="s" s="4">
-        <v>22</v>
-      </c>
-      <c r="N4" t="s" s="4">
-        <v>19</v>
-      </c>
-      <c r="O4" t="s" s="4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" t="s" s="4">
-        <v>30</v>
+      <c r="L4" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="M4" t="s" s="5">
+        <v>15</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" t="s" s="5">
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" t="s" s="4">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s" s="4">
-        <v>31</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s" s="4">
-        <v>32</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
   <si>
     <t>Data</t>
   </si>
@@ -31,9 +31,6 @@
     <t>Piano</t>
   </si>
   <si>
-    <t>Bass</t>
-  </si>
-  <si>
     <t>Chitarra</t>
   </si>
   <si>
@@ -70,25 +67,40 @@
     <t>Luigi</t>
   </si>
   <si>
+    <t>Giacomo</t>
+  </si>
+  <si>
+    <t>Alessia; Luigi</t>
+  </si>
+  <si>
     <t>Rav</t>
   </si>
   <si>
-    <t>Giacomo</t>
-  </si>
-  <si>
-    <t>Alessia; Luigi</t>
-  </si>
-  <si>
     <t>Luigi; Rav</t>
   </si>
   <si>
     <t>Angelo; Rav</t>
   </si>
   <si>
-    <t>Giacomo; Angelo; Alessia</t>
-  </si>
-  <si>
-    <t>Giacomo; Luigi</t>
+    <t>Miria</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t>Meilei, ChiaraW</t>
+  </si>
+  <si>
+    <t>Daniele</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Danny</t>
+  </si>
+  <si>
+    <t>David, Kevin</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1240,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17.6719" style="1" customWidth="1"/>
@@ -1237,12 +1249,11 @@
     <col min="4" max="4" width="20" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.35156" style="1" customWidth="1"/>
     <col min="6" max="6" width="7.85156" style="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="11" width="7.67188" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.8516" style="1" customWidth="1"/>
-    <col min="13" max="14" width="9.85156" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.3516" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="12.6719" style="1" customWidth="1"/>
+    <col min="7" max="10" width="7.67188" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.8516" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9.85156" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3516" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="12.6719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -1288,53 +1299,47 @@
       <c r="N1" t="s" s="3">
         <v>13</v>
       </c>
-      <c r="O1" t="s" s="3">
-        <v>14</v>
-      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4">
         <v>46187</v>
       </c>
       <c r="B2" t="s" s="5">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s" s="5">
         <v>15</v>
       </c>
-      <c r="C2" t="s" s="5">
+      <c r="D2" t="s" s="5">
         <v>16</v>
       </c>
-      <c r="D2" t="s" s="5">
+      <c r="E2" t="s" s="5">
         <v>17</v>
       </c>
-      <c r="E2" t="s" s="5">
-        <v>18</v>
-      </c>
       <c r="F2" t="s" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s" s="5">
         <v>18</v>
       </c>
       <c r="I2" t="s" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s" s="5">
-        <v>18</v>
-      </c>
-      <c r="M2" t="s" s="5">
-        <v>15</v>
-      </c>
-      <c r="N2" s="6"/>
-      <c r="O2" t="s" s="5">
-        <v>21</v>
+        <v>14</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" t="s" s="5">
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -1342,46 +1347,43 @@
         <v>46194</v>
       </c>
       <c r="B3" t="s" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s" s="5">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s" s="5">
         <v>18</v>
       </c>
       <c r="I3" t="s" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K3" t="s" s="5">
         <v>20</v>
       </c>
       <c r="L3" t="s" s="5">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M3" t="s" s="5">
         <v>15</v>
       </c>
       <c r="N3" t="s" s="5">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -1389,45 +1391,36 @@
         <v>46201</v>
       </c>
       <c r="B4" t="s" s="5">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s" s="5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s" s="5">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s" s="5">
-        <v>15</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E4" s="5"/>
       <c r="F4" t="s" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s" s="5">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s" s="5">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s" s="5">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s" s="5">
         <v>20</v>
       </c>
-      <c r="J4" t="s" s="5">
-        <v>19</v>
-      </c>
       <c r="K4" t="s" s="5">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s" s="5">
-        <v>15</v>
-      </c>
-      <c r="M4" t="s" s="5">
-        <v>15</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6"/>
       <c r="N4" s="6"/>
-      <c r="O4" t="s" s="5">
-        <v>25</v>
-      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4"/>
@@ -1442,9 +1435,8 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="6"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4"/>
@@ -1459,9 +1451,8 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -11,96 +11,330 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="108">
   <si>
     <t>Data</t>
   </si>
   <si>
-    <t>Parola</t>
-  </si>
-  <si>
-    <t>Adorazione</t>
-  </si>
-  <si>
-    <t>Coro</t>
-  </si>
-  <si>
-    <t>BimbiGiovani</t>
-  </si>
-  <si>
-    <t>Piano</t>
-  </si>
-  <si>
-    <t>Chitarra</t>
-  </si>
-  <si>
-    <t>Mix</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>Porta</t>
-  </si>
-  <si>
-    <t>Pulizia</t>
-  </si>
-  <si>
-    <t>Pulizia sala bimbi</t>
-  </si>
-  <si>
-    <t>Traduzione</t>
-  </si>
-  <si>
-    <t>Ronda</t>
+    <t>📖 Parola</t>
+  </si>
+  <si>
+    <t>🙌🏻 Adorazione</t>
+  </si>
+  <si>
+    <t>🎤 Coro</t>
+  </si>
+  <si>
+    <t>👩🏻‍🏫 Scuola Bimbi</t>
+  </si>
+  <si>
+    <t>👨🏻‍🏫 Adolescenti</t>
+  </si>
+  <si>
+    <t>🎹 Piano</t>
+  </si>
+  <si>
+    <t>🎸 Chitarra</t>
+  </si>
+  <si>
+    <t>🎻 Violino</t>
+  </si>
+  <si>
+    <t>🎛️ Mix</t>
+  </si>
+  <si>
+    <t>💻 PC</t>
+  </si>
+  <si>
+    <t>🚪 Porta</t>
+  </si>
+  <si>
+    <t>🧹 Pulizia</t>
+  </si>
+  <si>
+    <t>🧹 Pulizia Bimbi</t>
+  </si>
+  <si>
+    <t>🇨🇳🇮🇹 Traduzione</t>
+  </si>
+  <si>
+    <t>🛡️ Ronda</t>
+  </si>
+  <si>
+    <t>Culto sala grande</t>
+  </si>
+  <si>
+    <t>Alessia</t>
+  </si>
+  <si>
+    <t>Luana</t>
+  </si>
+  <si>
+    <t>Angelo, Giacomo</t>
+  </si>
+  <si>
+    <t>Sor. Miria</t>
+  </si>
+  <si>
+    <t>Jonni</t>
+  </si>
+  <si>
+    <t>ChiaraW, Luana, Miyu</t>
+  </si>
+  <si>
+    <t>Stefany, Angelo</t>
+  </si>
+  <si>
+    <t>Daniele</t>
+  </si>
+  <si>
+    <t>Betta</t>
+  </si>
+  <si>
+    <t>Davide</t>
+  </si>
+  <si>
+    <t>Danny</t>
+  </si>
+  <si>
+    <t>Rav</t>
+  </si>
+  <si>
+    <t>Luigi, Rav</t>
+  </si>
+  <si>
+    <t>Frat. Rav</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t>Meilei, Xinyi, Jonni</t>
+  </si>
+  <si>
+    <t>Cecilia, Angelo</t>
+  </si>
+  <si>
+    <t>Tonino</t>
+  </si>
+  <si>
+    <t>Giacomo</t>
+  </si>
+  <si>
+    <t>Ale</t>
+  </si>
+  <si>
+    <t>Luigi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angelo, Francesco </t>
+  </si>
+  <si>
+    <t>Pastore Gianluca</t>
+  </si>
+  <si>
+    <t>Xuelai, Paola, Daniele, Lidia</t>
+  </si>
+  <si>
+    <t>Angelo, Stefany</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Meilei, Anna</t>
+  </si>
+  <si>
+    <t>Chiara</t>
+  </si>
+  <si>
+    <t>Rav, Daniele</t>
+  </si>
+  <si>
+    <t>ChiaraW</t>
+  </si>
+  <si>
+    <t>Iris, Beibei, Jonni</t>
+  </si>
+  <si>
+    <t>Danny, Xuelai</t>
+  </si>
+  <si>
+    <t>DavideB</t>
+  </si>
+  <si>
+    <t>Federica, Oujie, Daniele</t>
+  </si>
+  <si>
+    <t>ChiaraZ, Stefany</t>
+  </si>
+  <si>
+    <t>Giacomo, Elia</t>
+  </si>
+  <si>
+    <t>Sor. Iris</t>
+  </si>
+  <si>
+    <t>Xuelei</t>
+  </si>
+  <si>
+    <t>Meilei, Paola, Elia</t>
+  </si>
+  <si>
+    <t>Jonni, Weiwei</t>
+  </si>
+  <si>
+    <t>SALA GRANDE</t>
+  </si>
+  <si>
+    <t>Oujie, Luana, Jonni</t>
+  </si>
+  <si>
+    <t>ChiaraZ</t>
+  </si>
+  <si>
+    <t>Xinyi</t>
+  </si>
+  <si>
+    <t>Jonni, Luigi</t>
+  </si>
+  <si>
+    <t>Maestro Pan</t>
+  </si>
+  <si>
+    <t>Meilei</t>
+  </si>
+  <si>
+    <t>ChiaraW, Alessia, Elia</t>
+  </si>
+  <si>
+    <t>Ariel</t>
+  </si>
+  <si>
+    <t>Elia</t>
+  </si>
+  <si>
+    <t>Vale</t>
+  </si>
+  <si>
+    <t>Alessandro, Paola</t>
+  </si>
+  <si>
+    <t>Sor. Ariel</t>
+  </si>
+  <si>
+    <t>Paola</t>
+  </si>
+  <si>
+    <t>Iris, Beibei, Daniele, Weiwei</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federica, Kevin </t>
+  </si>
+  <si>
+    <t>Oujie</t>
+  </si>
+  <si>
+    <t>Elisabetta</t>
+  </si>
+  <si>
+    <t>Federica, Paola, Daniele</t>
+  </si>
+  <si>
+    <t>Roberto, Cecilia</t>
   </si>
   <si>
     <t>Angelo</t>
   </si>
   <si>
-    <t>Alessia</t>
-  </si>
-  <si>
-    <t>Rav; Giacomo</t>
-  </si>
-  <si>
-    <t>Luigi</t>
-  </si>
-  <si>
-    <t>Giacomo</t>
-  </si>
-  <si>
-    <t>Alessia; Luigi</t>
-  </si>
-  <si>
-    <t>Rav</t>
-  </si>
-  <si>
-    <t>Luigi; Rav</t>
-  </si>
-  <si>
-    <t>Angelo; Rav</t>
-  </si>
-  <si>
-    <t>Miria</t>
-  </si>
-  <si>
-    <t>Iris</t>
-  </si>
-  <si>
-    <t>Meilei, ChiaraW</t>
-  </si>
-  <si>
-    <t>Daniele</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Danny</t>
+    <t>Meilei, Xinyi, Elia</t>
+  </si>
+  <si>
+    <t>Giulio</t>
+  </si>
+  <si>
+    <t>Alessia, Paola, Jonni</t>
+  </si>
+  <si>
+    <t>Stef, Angelo</t>
+  </si>
+  <si>
+    <t>Rui, Daniele</t>
+  </si>
+  <si>
+    <t>吴建辉</t>
+  </si>
+  <si>
+    <t>Aurora Hu, Cecilia</t>
+  </si>
+  <si>
+    <t>Iris, Beibei, Miyu</t>
+  </si>
+  <si>
+    <t>Angelo, Stef</t>
+  </si>
+  <si>
+    <t>Luana, Meilei</t>
+  </si>
+  <si>
+    <t>Elia, Kevin</t>
+  </si>
+  <si>
+    <t>Paola, Luana, Lidia</t>
+  </si>
+  <si>
+    <t>Iris, Lidia</t>
+  </si>
+  <si>
+    <t>Sor. Anna</t>
+  </si>
+  <si>
+    <t>Alessia, Xinyi, Elia</t>
+  </si>
+  <si>
+    <t>Luana, Paola</t>
+  </si>
+  <si>
+    <t>Tonino, Betta</t>
+  </si>
+  <si>
+    <t>LucaW, Luigi</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>Sor. Xinyi</t>
+  </si>
+  <si>
+    <t>Alessia, Oujie</t>
+  </si>
+  <si>
+    <t>Oujie, Xuelai, Jonni</t>
+  </si>
+  <si>
+    <t>Roberto, Luca</t>
+  </si>
+  <si>
+    <t>Iris, Beibei, Weiwei</t>
+  </si>
+  <si>
+    <t>Lujing, Federica</t>
+  </si>
+  <si>
+    <t>Federica, Oujie, Daniele, Miyu</t>
+  </si>
+  <si>
+    <t>LucaW, Elia</t>
   </si>
   <si>
     <t>David, Kevin</t>
+  </si>
+  <si>
+    <t>Francesco</t>
   </si>
 </sst>
 </file>
@@ -111,11 +345,16 @@
     <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="59" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
     </font>
     <font>
       <sz val="15"/>
@@ -173,10 +412,7 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="59" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -187,6 +423,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="59" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1240,207 +1479,232 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.6719" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.8516" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1719" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.35156" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.85156" style="1" customWidth="1"/>
-    <col min="7" max="10" width="7.67188" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.8516" style="1" customWidth="1"/>
-    <col min="12" max="13" width="9.85156" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.3516" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="12.6719" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6719" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6719" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.35156" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.8516" style="1" customWidth="1"/>
+    <col min="5" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.8516" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.35156" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.67188" style="1" customWidth="1"/>
+    <col min="11" max="11" width="5.85156" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.67188" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.8516" style="1" customWidth="1"/>
+    <col min="14" max="14" width="11.3516" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.85156" style="1" customWidth="1"/>
+    <col min="16" max="16" width="13.3516" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="12.6719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="3">
+      <c r="B1" t="s" s="2">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
+      <c r="C1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="3">
+      <c r="D1" t="s" s="2">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="3">
+      <c r="E1" t="s" s="2">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="3">
+      <c r="F1" t="s" s="2">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="3">
+      <c r="G1" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="3">
+      <c r="H1" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="3">
+      <c r="I1" t="s" s="2">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="3">
+      <c r="J1" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="3">
+      <c r="K1" t="s" s="2">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="3">
+      <c r="L1" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="3">
+      <c r="M1" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="N1" t="s" s="3">
+      <c r="N1" t="s" s="2">
         <v>13</v>
       </c>
+      <c r="O1" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4">
-        <v>46187</v>
-      </c>
-      <c r="B2" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s" s="5">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s" s="5">
+      <c r="A2" s="3">
+        <v>46208</v>
+      </c>
+      <c r="B2" t="s" s="4">
         <v>16</v>
       </c>
-      <c r="E2" t="s" s="5">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="F2" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s" s="5">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s" s="5">
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" t="s" s="4">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="5">
+      <c r="P2" t="s" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="3">
+        <v>46215</v>
+      </c>
+      <c r="B3" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s" s="4">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" t="s" s="4">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s" s="4">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="4">
+        <v>29</v>
+      </c>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="3">
+        <v>46222</v>
+      </c>
+      <c r="B4" t="s" s="4">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s" s="4">
+        <v>32</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="H4" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="3">
+        <v>46229</v>
+      </c>
+      <c r="B5" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s" s="4">
         <v>18</v>
       </c>
-      <c r="J2" t="s" s="5">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s" s="5">
-        <v>17</v>
-      </c>
-      <c r="L2" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="M2" s="6"/>
-      <c r="N2" t="s" s="5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4">
-        <v>46194</v>
-      </c>
-      <c r="B3" t="s" s="5">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s" s="5">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s" s="5">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s" s="5">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s" s="5">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s" s="5">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s" s="5">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s" s="5">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s" s="5">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="M3" t="s" s="5">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4">
-        <v>46201</v>
-      </c>
-      <c r="B4" t="s" s="5">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s" s="5">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s" s="5">
-        <v>25</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" t="s" s="5">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s" s="5">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s" s="5">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s" s="5">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s" s="5">
-        <v>20</v>
-      </c>
-      <c r="K4" t="s" s="5">
-        <v>29</v>
-      </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="D5" t="s" s="4">
+        <v>40</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
+      <c r="G5" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I5" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s" s="4">
+        <v>43</v>
+      </c>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="3">
+        <v>46236</v>
+      </c>
+      <c r="B6" t="s" s="4">
+        <v>16</v>
+      </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -1450,15 +1714,953 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
+      <c r="L6" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" t="s" s="4">
+        <v>44</v>
+      </c>
+      <c r="P6" t="s" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="3">
+        <v>46243</v>
+      </c>
+      <c r="B7" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s" s="4">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s" s="4">
+        <v>47</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" t="s" s="4">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J7" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="K7" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="M7" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="6">
+        <v>46250</v>
+      </c>
+      <c r="B8" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="6">
+        <v>46257</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s" s="4">
+        <v>50</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I9" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J9" t="s" s="4">
+        <v>26</v>
+      </c>
+      <c r="K9" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="L9" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="M9" t="s" s="4">
+        <v>52</v>
+      </c>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="3">
+        <v>46264</v>
+      </c>
+      <c r="B10" t="s" s="4">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s" s="4">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s" s="4">
+        <v>55</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K10" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="L10" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="M10" t="s" s="4">
+        <v>56</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="P10" s="5"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="3">
+        <v>46264</v>
+      </c>
+      <c r="B11" t="s" s="4">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="H11" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I11" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="3">
+        <v>46271</v>
+      </c>
+      <c r="B12" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="F12" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" t="s" s="4">
+        <v>60</v>
+      </c>
+      <c r="P12" t="s" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="3">
+        <v>46278</v>
+      </c>
+      <c r="B13" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="D13" t="s" s="4">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s" s="4">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I13" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J13" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="K13" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="L13" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="M13" t="s" s="4">
+        <v>68</v>
+      </c>
+      <c r="N13" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="O13" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="P13" s="5"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="3">
+        <v>46285</v>
+      </c>
+      <c r="B14" t="s" s="4">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s" s="4">
+        <v>70</v>
+      </c>
+      <c r="D14" t="s" s="4">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="F14" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="G14" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="H14" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J14" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="K14" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="L14" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="M14" t="s" s="4">
+        <v>73</v>
+      </c>
+      <c r="N14" t="s" s="4">
+        <v>74</v>
+      </c>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="3">
+        <v>46292</v>
+      </c>
+      <c r="B15" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s" s="4">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s" s="4">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="F15" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="G15" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="H15" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I15" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J15" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K15" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="L15" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="M15" t="s" s="4">
+        <v>77</v>
+      </c>
+      <c r="N15" t="s" s="4">
+        <v>78</v>
+      </c>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="3">
+        <v>46299</v>
+      </c>
+      <c r="B16" t="s" s="4">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s" s="4">
+        <v>74</v>
+      </c>
+      <c r="D16" t="s" s="4">
+        <v>79</v>
+      </c>
+      <c r="E16" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="F16" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="G16" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="H16" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s" s="4">
+        <v>80</v>
+      </c>
+      <c r="P16" t="s" s="4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="3">
+        <v>46306</v>
+      </c>
+      <c r="B17" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="G17" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="H17" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I17" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J17" t="s" s="4">
+        <v>26</v>
+      </c>
+      <c r="K17" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="L17" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="M17" t="s" s="4">
+        <v>83</v>
+      </c>
+      <c r="N17" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="3">
+        <v>46313</v>
+      </c>
+      <c r="B18" t="s" s="4">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s" s="4">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s" s="4">
+        <v>60</v>
+      </c>
+      <c r="F18" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="G18" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="H18" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I18" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J18" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="K18" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="L18" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="M18" t="s" s="4">
+        <v>85</v>
+      </c>
+      <c r="N18" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="O18" t="s" s="4">
+        <v>80</v>
+      </c>
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="3">
+        <v>46320</v>
+      </c>
+      <c r="B19" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s" s="4">
+        <v>86</v>
+      </c>
+      <c r="E19" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="F19" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="G19" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="H19" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I19" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J19" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K19" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="L19" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="M19" t="s" s="4">
+        <v>88</v>
+      </c>
+      <c r="N19" t="s" s="4">
+        <v>60</v>
+      </c>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="3">
+        <v>46327</v>
+      </c>
+      <c r="B20" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="O20" t="s" s="4">
+        <v>74</v>
+      </c>
+      <c r="P20" t="s" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3">
+        <v>46334</v>
+      </c>
+      <c r="B21" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="E21" t="s" s="4">
+        <v>74</v>
+      </c>
+      <c r="F21" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="G21" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="H21" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I21" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J21" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="K21" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="L21" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="M21" t="s" s="4">
+        <v>91</v>
+      </c>
+      <c r="N21" t="s" s="4">
+        <v>70</v>
+      </c>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="3">
+        <v>46341</v>
+      </c>
+      <c r="B22" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="C22" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s" s="4">
+        <v>93</v>
+      </c>
+      <c r="E22" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="F22" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="G22" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="H22" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I22" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J22" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="K22" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="L22" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="M22" t="s" s="4">
+        <v>94</v>
+      </c>
+      <c r="N22" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="3">
+        <v>46348</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" t="s" s="4">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s" s="4">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="F23" t="s" s="4">
+        <v>95</v>
+      </c>
+      <c r="G23" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="H23" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I23" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J23" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K23" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="L23" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="M23" t="s" s="4">
+        <v>96</v>
+      </c>
+      <c r="N23" t="s" s="4">
+        <v>97</v>
+      </c>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="3">
+        <v>46355</v>
+      </c>
+      <c r="B24" t="s" s="4">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="F24" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="G24" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="H24" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I24" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J24" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K24" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="L24" t="s" s="4">
+        <v>78</v>
+      </c>
+      <c r="M24" t="s" s="4">
+        <v>99</v>
+      </c>
+      <c r="N24" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="O24" t="s" s="4">
+        <v>74</v>
+      </c>
+      <c r="P24" s="5"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="3">
+        <v>46362</v>
+      </c>
+      <c r="B25" t="s" s="4">
+        <v>57</v>
+      </c>
+      <c r="C25" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="D25" t="s" s="4">
+        <v>100</v>
+      </c>
+      <c r="E25" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="F25" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="G25" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="H25" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="K25" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="L25" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="O25" t="s" s="4">
+        <v>60</v>
+      </c>
+      <c r="P25" t="s" s="4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="3">
+        <v>46369</v>
+      </c>
+      <c r="B26" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="C26" t="s" s="4">
+        <v>70</v>
+      </c>
+      <c r="D26" t="s" s="4">
+        <v>102</v>
+      </c>
+      <c r="E26" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="F26" t="s" s="4">
+        <v>65</v>
+      </c>
+      <c r="G26" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="H26" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I26" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J26" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K26" t="s" s="4">
+        <v>27</v>
+      </c>
+      <c r="L26" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="M26" t="s" s="4">
+        <v>103</v>
+      </c>
+      <c r="N26" t="s" s="4">
+        <v>46</v>
+      </c>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="3">
+        <v>46376</v>
+      </c>
+      <c r="B27" t="s" s="4">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s" s="4">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s" s="4">
+        <v>104</v>
+      </c>
+      <c r="E27" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="F27" t="s" s="4">
+        <v>95</v>
+      </c>
+      <c r="G27" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="H27" t="s" s="4">
+        <v>24</v>
+      </c>
+      <c r="I27" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J27" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="K27" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="L27" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="M27" t="s" s="4">
+        <v>105</v>
+      </c>
+      <c r="N27" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="3">
+        <v>46383</v>
+      </c>
+      <c r="B28" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="C28" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s" s="4">
+        <v>79</v>
+      </c>
+      <c r="E28" t="s" s="4">
+        <v>74</v>
+      </c>
+      <c r="F28" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="G28" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="H28" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="I28" t="s" s="4">
+        <v>25</v>
+      </c>
+      <c r="J28" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="K28" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="L28" t="s" s="4">
+        <v>28</v>
+      </c>
+      <c r="M28" t="s" s="4">
+        <v>106</v>
+      </c>
+      <c r="N28" t="s" s="4">
+        <v>107</v>
+      </c>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="overThenDown"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Arial,Regular"&amp;10&amp;K000000000000&amp;P</oddFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/turni.xlsx
+++ b/turni.xlsx
@@ -130,97 +130,97 @@
     <t xml:space="preserve">Angelo, Francesco </t>
   </si>
   <si>
+    <t>Sor. Ariel</t>
+  </si>
+  <si>
+    <t>Xuelai, Paola, Daniele, Lidia</t>
+  </si>
+  <si>
+    <t>Angelo, Stefany</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Meilei, Anna</t>
+  </si>
+  <si>
+    <t>Chiara</t>
+  </si>
+  <si>
+    <t>Rav, Daniele</t>
+  </si>
+  <si>
+    <t>ChiaraW</t>
+  </si>
+  <si>
+    <t>Iris, Beibei, Jonni</t>
+  </si>
+  <si>
+    <t>Danny, Xuelai</t>
+  </si>
+  <si>
+    <t>DavideB</t>
+  </si>
+  <si>
+    <t>Federica, Oujie, Daniele</t>
+  </si>
+  <si>
+    <t>ChiaraZ, Stefany</t>
+  </si>
+  <si>
+    <t>Giacomo, Elia</t>
+  </si>
+  <si>
+    <t>Sor. Iris</t>
+  </si>
+  <si>
+    <t>Xuelei</t>
+  </si>
+  <si>
+    <t>Meilei, Paola, Elia</t>
+  </si>
+  <si>
+    <t>Jonni, Weiwei</t>
+  </si>
+  <si>
+    <t>SALA GRANDE</t>
+  </si>
+  <si>
+    <t>Oujie, Luana, Jonni</t>
+  </si>
+  <si>
+    <t>ChiaraZ</t>
+  </si>
+  <si>
+    <t>Xinyi</t>
+  </si>
+  <si>
+    <t>Jonni, Luigi</t>
+  </si>
+  <si>
+    <t>Maestro Pan</t>
+  </si>
+  <si>
+    <t>Meilei</t>
+  </si>
+  <si>
+    <t>ChiaraW, Alessia, Elia</t>
+  </si>
+  <si>
+    <t>Ariel</t>
+  </si>
+  <si>
+    <t>Elia</t>
+  </si>
+  <si>
+    <t>Vale</t>
+  </si>
+  <si>
+    <t>Alessandro, Paola</t>
+  </si>
+  <si>
     <t>Pastore Gianluca</t>
-  </si>
-  <si>
-    <t>Xuelai, Paola, Daniele, Lidia</t>
-  </si>
-  <si>
-    <t>Angelo, Stefany</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Meilei, Anna</t>
-  </si>
-  <si>
-    <t>Chiara</t>
-  </si>
-  <si>
-    <t>Rav, Daniele</t>
-  </si>
-  <si>
-    <t>ChiaraW</t>
-  </si>
-  <si>
-    <t>Iris, Beibei, Jonni</t>
-  </si>
-  <si>
-    <t>Danny, Xuelai</t>
-  </si>
-  <si>
-    <t>DavideB</t>
-  </si>
-  <si>
-    <t>Federica, Oujie, Daniele</t>
-  </si>
-  <si>
-    <t>ChiaraZ, Stefany</t>
-  </si>
-  <si>
-    <t>Giacomo, Elia</t>
-  </si>
-  <si>
-    <t>Sor. Iris</t>
-  </si>
-  <si>
-    <t>Xuelei</t>
-  </si>
-  <si>
-    <t>Meilei, Paola, Elia</t>
-  </si>
-  <si>
-    <t>Jonni, Weiwei</t>
-  </si>
-  <si>
-    <t>SALA GRANDE</t>
-  </si>
-  <si>
-    <t>Oujie, Luana, Jonni</t>
-  </si>
-  <si>
-    <t>ChiaraZ</t>
-  </si>
-  <si>
-    <t>Xinyi</t>
-  </si>
-  <si>
-    <t>Jonni, Luigi</t>
-  </si>
-  <si>
-    <t>Maestro Pan</t>
-  </si>
-  <si>
-    <t>Meilei</t>
-  </si>
-  <si>
-    <t>ChiaraW, Alessia, Elia</t>
-  </si>
-  <si>
-    <t>Ariel</t>
-  </si>
-  <si>
-    <t>Elia</t>
-  </si>
-  <si>
-    <t>Vale</t>
-  </si>
-  <si>
-    <t>Alessandro, Paola</t>
-  </si>
-  <si>
-    <t>Sor. Ariel</t>
   </si>
   <si>
     <t>Paola</t>
@@ -2213,7 +2213,7 @@
         <v>46320</v>
       </c>
       <c r="B19" t="s" s="4">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s" s="4">
         <v>66</v>
@@ -2569,7 +2569,7 @@
         <v>46376</v>
       </c>
       <c r="B27" t="s" s="4">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s" s="4">
         <v>17</v>
@@ -2615,7 +2615,7 @@
         <v>46383</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s" s="4">
         <v>31</v>

--- a/turni.xlsx
+++ b/turni.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="109">
   <si>
     <t>Data</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Federica, Paola, Daniele</t>
+  </si>
+  <si>
+    <t>Angelo, Cecilia</t>
   </si>
   <si>
     <t>Roberto, Cecilia</t>
@@ -1952,7 +1955,7 @@
         <v>65</v>
       </c>
       <c r="G13" t="s" s="4">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H13" t="s" s="4">
         <v>34</v>
@@ -2046,7 +2049,7 @@
         <v>66</v>
       </c>
       <c r="G15" t="s" s="4">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="4">
         <v>34</v>
@@ -2064,10 +2067,10 @@
         <v>28</v>
       </c>
       <c r="M15" t="s" s="4">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N15" t="s" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O15" s="5"/>
       <c r="P15" s="5"/>
@@ -2083,7 +2086,7 @@
         <v>74</v>
       </c>
       <c r="D16" t="s" s="4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s" s="4">
         <v>72</v>
@@ -2108,7 +2111,7 @@
         <v>21</v>
       </c>
       <c r="O16" t="s" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P16" t="s" s="4">
         <v>19</v>
@@ -2125,7 +2128,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="s" s="4">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s" s="4">
         <v>31</v>
@@ -2134,7 +2137,7 @@
         <v>35</v>
       </c>
       <c r="G17" t="s" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s" s="4">
         <v>34</v>
@@ -2152,7 +2155,7 @@
         <v>37</v>
       </c>
       <c r="M17" t="s" s="4">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N17" t="s" s="4">
         <v>28</v>
@@ -2165,7 +2168,7 @@
         <v>46313</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s" s="4">
         <v>24</v>
@@ -2198,13 +2201,13 @@
         <v>35</v>
       </c>
       <c r="M18" t="s" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N18" t="s" s="4">
         <v>31</v>
       </c>
       <c r="O18" t="s" s="4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P18" s="5"/>
     </row>
@@ -2219,7 +2222,7 @@
         <v>66</v>
       </c>
       <c r="D19" t="s" s="4">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s" s="4">
         <v>72</v>
@@ -2228,7 +2231,7 @@
         <v>28</v>
       </c>
       <c r="G19" t="s" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="4">
         <v>34</v>
@@ -2246,7 +2249,7 @@
         <v>28</v>
       </c>
       <c r="M19" t="s" s="4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N19" t="s" s="4">
         <v>60</v>
@@ -2285,7 +2288,7 @@
         <v>74</v>
       </c>
       <c r="P20" t="s" s="4">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -2299,7 +2302,7 @@
         <v>21</v>
       </c>
       <c r="D21" t="s" s="4">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s" s="4">
         <v>74</v>
@@ -2308,7 +2311,7 @@
         <v>35</v>
       </c>
       <c r="G21" t="s" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="4">
         <v>24</v>
@@ -2326,7 +2329,7 @@
         <v>37</v>
       </c>
       <c r="M21" t="s" s="4">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N21" t="s" s="4">
         <v>70</v>
@@ -2339,13 +2342,13 @@
         <v>46341</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s" s="4">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="4">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s" s="4">
         <v>37</v>
@@ -2372,7 +2375,7 @@
         <v>35</v>
       </c>
       <c r="M22" t="s" s="4">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N22" t="s" s="4">
         <v>63</v>
@@ -2395,10 +2398,10 @@
         <v>72</v>
       </c>
       <c r="F23" t="s" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s" s="4">
         <v>24</v>
@@ -2416,10 +2419,10 @@
         <v>28</v>
       </c>
       <c r="M23" t="s" s="4">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N23" t="s" s="4">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O23" s="5"/>
       <c r="P23" s="5"/>
@@ -2429,13 +2432,13 @@
         <v>46355</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s" s="4">
         <v>65</v>
       </c>
       <c r="D24" t="s" s="4">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s" s="4">
         <v>31</v>
@@ -2459,10 +2462,10 @@
         <v>67</v>
       </c>
       <c r="L24" t="s" s="4">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M24" t="s" s="4">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N24" t="s" s="4">
         <v>21</v>
@@ -2483,7 +2486,7 @@
         <v>63</v>
       </c>
       <c r="D25" t="s" s="4">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s" s="4">
         <v>72</v>
@@ -2515,7 +2518,7 @@
         <v>60</v>
       </c>
       <c r="P25" t="s" s="4">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -2529,7 +2532,7 @@
         <v>70</v>
       </c>
       <c r="D26" t="s" s="4">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E26" t="s" s="4">
         <v>37</v>
@@ -2538,7 +2541,7 @@
         <v>65</v>
       </c>
       <c r="G26" t="s" s="4">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="4">
         <v>34</v>
@@ -2556,7 +2559,7 @@
         <v>37</v>
       </c>
       <c r="M26" t="s" s="4">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N26" t="s" s="4">
         <v>46</v>
@@ -2575,13 +2578,13 @@
         <v>17</v>
       </c>
       <c r="D27" t="s" s="4">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s" s="4">
         <v>72</v>
       </c>
       <c r="F27" t="s" s="4">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s" s="4">
         <v>33</v>
@@ -2602,7 +2605,7 @@
         <v>35</v>
       </c>
       <c r="M27" t="s" s="4">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N27" t="s" s="4">
         <v>72</v>
@@ -2621,7 +2624,7 @@
         <v>31</v>
       </c>
       <c r="D28" t="s" s="4">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s" s="4">
         <v>74</v>
@@ -2630,7 +2633,7 @@
         <v>35</v>
       </c>
       <c r="G28" t="s" s="4">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="4">
         <v>34</v>
@@ -2648,10 +2651,10 @@
         <v>28</v>
       </c>
       <c r="M28" t="s" s="4">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N28" t="s" s="4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
